--- a/experiment/ELAN_bestx2/Test/results-Set5/Set5.xlsx
+++ b/experiment/ELAN_bestx2/Test/results-Set5/Set5.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>37.95</v>
+        <v>38.89</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9615</v>
+        <v>0.9679</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38.27</v>
+        <v>43.04</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9794</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.55</v>
+        <v>35.21</v>
       </c>
       <c r="C4" t="n">
-        <v>0.928</v>
+        <v>0.9771</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35.43</v>
+        <v>36</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8804</v>
+        <v>0.8907</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33.34</v>
+        <v>36.44</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9583</v>
+        <v>0.9747</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34.71</v>
+        <v>37.91</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9415</v>
+        <v>0.9601</v>
       </c>
     </row>
   </sheetData>
